--- a/artfynd/A 28577-2024 artfynd.xlsx
+++ b/artfynd/A 28577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117766453</v>
+        <v>117766459</v>
       </c>
       <c r="B2" t="n">
-        <v>96873</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>824377</v>
+        <v>824483</v>
       </c>
       <c r="R2" t="n">
-        <v>7370268</v>
+        <v>7370220</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,12 +784,7 @@
         <v>117766457</v>
       </c>
       <c r="B3" t="n">
-        <v>96801</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,6 +884,1066 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117766449</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>824422</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370266</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117766451</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>824385</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370289</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117766453</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>824377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7370268</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117766455</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>824517</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7370194</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117766461</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>824421</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7370286</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>117766464</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>824408</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370278</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>117766466</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>824365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370303</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>117766468</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>824480</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7370199</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>117766470</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>824500</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370159</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>117766472</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Talljärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>824501</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370166</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28577-2024 artfynd.xlsx
+++ b/artfynd/A 28577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766459</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766457</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766451</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766453</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766455</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766461</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766464</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766466</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766468</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766470</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,8 +2004,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>